--- a/ig/tru-exemples/CodeSystem-fr-core-cs-schedule-type.xlsx
+++ b/ig/tru-exemples/CodeSystem-fr-core-cs-schedule-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:26:02+00:00</t>
+    <t>2024-03-11T15:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/tru-exemples/CodeSystem-fr-core-cs-schedule-type.xlsx
+++ b/ig/tru-exemples/CodeSystem-fr-core-cs-schedule-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T15:09:21+00:00</t>
+    <t>2024-03-11T15:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
